--- a/Data/EXCEL/Transfer/salemon/202412/6594-salemon-202412.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202412/6594-salemon-202412.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\202412\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202412\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0449110-D965-41F8-9243-ABAD1B435DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDC1C475-D61F-466F-92A0-7B6583012E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{3DEF4AA7-1FDC-47DE-9555-79698FC0828F}"/>
+    <workbookView xWindow="2235" yWindow="1695" windowWidth="21600" windowHeight="13425" xr2:uid="{D6BCD6A5-BD50-4E38-B959-414BB59E417B}"/>
   </bookViews>
   <sheets>
     <sheet name="6594-salemon-202412" sheetId="2" r:id="rId1"/>
@@ -1255,25 +1255,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03204062-7499-4962-9270-D5426964875F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA2DDE52-E369-4461-815A-D0944CF5E393}">
   <dimension ref="A1:Q22"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" customWidth="1"/>
-    <col min="2" max="5" width="14.54296875" customWidth="1"/>
-    <col min="6" max="6" width="13.81640625" customWidth="1"/>
-    <col min="7" max="7" width="16.08984375" customWidth="1"/>
-    <col min="8" max="8" width="14.54296875" customWidth="1"/>
-    <col min="9" max="10" width="13.81640625" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" customWidth="1"/>
-    <col min="12" max="12" width="13.81640625" customWidth="1"/>
-    <col min="13" max="13" width="14.54296875" customWidth="1"/>
-    <col min="14" max="15" width="13.81640625" customWidth="1"/>
-    <col min="16" max="16" width="14.54296875" customWidth="1"/>
-    <col min="17" max="17" width="14.90625" customWidth="1"/>
+    <col min="1" max="1" width="11.875" customWidth="1"/>
+    <col min="2" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="9.5" customWidth="1"/>
+    <col min="7" max="7" width="10.875" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="9.5" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="15" width="9.5" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1300,7 +1300,7 @@
       <c r="P1" s="20"/>
       <c r="Q1" s="21"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
       <c r="B2" s="16" t="s">
         <v>4</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Q2" s="21"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -1382,7 +1382,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1421,7 +1421,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>44958</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>-76.5</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>44927</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>-78.3</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>44896</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>-7.72</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>44866</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>44835</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>9.02</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>44805</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>44774</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>44743</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>33.299999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>44713</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>38.1</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>44682</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>44652</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>42.7</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>44621</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>46.5</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>44593</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>42.4</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>44562</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>41.1</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>44531</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>-3.47</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>44501</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>-6.05</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>44470</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>-6.95</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>44440</v>
       </c>
